--- a/conformance/fixtures/067-input-missing-required-error/template.xlsx
+++ b/conformance/fixtures/067-input-missing-required-error/template.xlsx
@@ -4,8 +4,8 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <sheets>
-    <sheet sheetId="1" name="_config" state="hidden" r:id="rId4"/>
-    <sheet sheetId="2" name="_inputs" state="hidden" r:id="rId5"/>
+    <sheet sheetId="1" name="__config__" state="hidden" r:id="rId4"/>
+    <sheet sheetId="2" name="__inputs__" state="hidden" r:id="rId5"/>
     <sheet sheetId="3" name="Report" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr calcId="171027"/>
@@ -54,7 +54,7 @@
     <t>Region</t>
   </si>
   <si>
-    <t>{{ _region }}</t>
+    <t>{{ __inputs__[region] }}</t>
   </si>
 </sst>
 </file>
